--- a/crates/xlstream-eval/tests/fixtures/math/arithmetic_math.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/math/arithmetic_math.xlsx
@@ -22,10 +22,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
-    <t xml:space="preserve">id</t>
+    <t xml:space="preserve">val</t>
   </si>
   <si>
-    <t xml:space="preserve">mod</t>
+    <t xml:space="preserve">mod3</t>
   </si>
   <si>
     <t xml:space="preserve">abs</t>
@@ -34,10 +34,10 @@
     <t xml:space="preserve">sign</t>
   </si>
   <si>
-    <t xml:space="preserve">sqrt</t>
+    <t xml:space="preserve">sqrt_abs</t>
   </si>
   <si>
-    <t xml:space="preserve">power</t>
+    <t xml:space="preserve">power2</t>
   </si>
 </sst>
 </file>
@@ -360,52 +360,52 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="B3" s="0" t="n">
         <f aca="false">MOD(A3,3)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" s="0" t="n">
         <f aca="false">ABS(A3)</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D3" s="0" t="n">
         <f aca="false">SIGN(A3)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="0" t="n">
         <f aca="false">SQRT(ABS(A3))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F3" s="0" t="n">
         <f aca="false">POWER(ABS(A3),2)</f>
-        <v>625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="B4" s="0" t="n">
         <f aca="false">MOD(A4,3)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4" s="0" t="n">
         <f aca="false">ABS(A4)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D4" s="0" t="n">
         <f aca="false">SIGN(A4)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E4" s="0" t="n">
         <f aca="false">SQRT(ABS(A4))</f>
-        <v>0</v>
+        <v>2.64575131106459</v>
       </c>
       <c r="F4" s="0" t="n">
         <f aca="false">POWER(ABS(A4),2)</f>
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -435,36 +435,36 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="B6" s="0" t="n">
         <f aca="false">MOD(A6,3)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="0" t="n">
         <f aca="false">ABS(A6)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" s="0" t="n">
         <f aca="false">SIGN(A6)</f>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E6" s="0" t="n">
         <f aca="false">SQRT(ABS(A6))</f>
-        <v>2.23606797749979</v>
+        <v>1.73205080756888</v>
       </c>
       <c r="F6" s="0" t="n">
         <f aca="false">POWER(ABS(A6),2)</f>
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="B7" s="0" t="n">
         <f aca="false">MOD(A7,3)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="0" t="n">
         <f aca="false">ABS(A7)</f>
@@ -472,7 +472,7 @@
       </c>
       <c r="D7" s="0" t="n">
         <f aca="false">SIGN(A7)</f>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E7" s="0" t="n">
         <f aca="false">SQRT(ABS(A7))</f>
@@ -485,15 +485,15 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="B8" s="0" t="n">
         <f aca="false">MOD(A8,3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="0" t="n">
         <f aca="false">ABS(A8)</f>
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="D8" s="0" t="n">
         <f aca="false">SIGN(A8)</f>
@@ -501,11 +501,11 @@
       </c>
       <c r="E8" s="0" t="n">
         <f aca="false">SQRT(ABS(A8))</f>
-        <v>8.66025403784439</v>
+        <v>5</v>
       </c>
       <c r="F8" s="0" t="n">
         <f aca="false">POWER(ABS(A8),2)</f>
-        <v>5625</v>
+        <v>625</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -560,27 +560,27 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="n">
-        <v>42</v>
+        <v>-1</v>
       </c>
       <c r="B11" s="0" t="n">
         <f aca="false">MOD(A11,3)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C11" s="0" t="n">
         <f aca="false">ABS(A11)</f>
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="D11" s="0" t="n">
         <f aca="false">SIGN(A11)</f>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E11" s="0" t="n">
         <f aca="false">SQRT(ABS(A11))</f>
-        <v>6.48074069840786</v>
+        <v>1</v>
       </c>
       <c r="F11" s="0" t="n">
         <f aca="false">POWER(ABS(A11),2)</f>
-        <v>1764</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
